--- a/InputData/elec/GBSC/cn-Grid Battery Storage Capacities.xlsx
+++ b/InputData/elec/GBSC/cn-Grid Battery Storage Capacities.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPS Repos\National Models\eps-china2019-smart-trans\InputData\elec\GBSC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="723" activeTab="7"/>
+    <workbookView windowWidth="23152" windowHeight="10605" tabRatio="723" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="13" r:id="rId1"/>
@@ -95,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="302">
   <si>
     <t>Grid Battery Storage Capacities</t>
   </si>
@@ -1517,6 +1522,21 @@
   </si>
   <si>
     <t>*From 2022: copied from 2022 national model</t>
+  </si>
+  <si>
+    <t>十五五情景规划值</t>
+  </si>
+  <si>
+    <t>Potential Additional</t>
+  </si>
+  <si>
+    <t>Potential Additional %</t>
+  </si>
+  <si>
+    <t>FOPITY</t>
+  </si>
+  <si>
+    <t>Max</t>
   </si>
   <si>
     <t>CNESA重磅｜2022储能产业盘点：大势已成，因势而动</t>
@@ -1656,9 +1676,6 @@
   </si>
   <si>
     <t>Maximum PAGBSC (percentage)</t>
-  </si>
-  <si>
-    <t>FOPITY</t>
   </si>
   <si>
     <t>Conservative Scenario</t>
@@ -2076,18 +2093,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="55">
+  <fills count="54">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2115,12 +2132,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2920,7 +2931,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2944,16 +2955,16 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2962,120 +2973,120 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="36" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="25" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="25">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="41" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="53" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="52" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3086,7 +3097,7 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="28">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="41" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="29" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
@@ -3097,9 +3108,9 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="46" fillId="42" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="48" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="48" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
@@ -3109,8 +3120,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="43" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="41" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="42" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="49" fillId="40" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="36" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
@@ -3196,13 +3207,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -3217,10 +3228,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3244,13 +3255,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="177" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -3372,7 +3383,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -11591,7 +11602,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:44">
       <c r="A1" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1">
         <v>2018</v>
@@ -11725,7 +11736,7 @@
     </row>
     <row r="2" s="2" customFormat="1" spans="1:44">
       <c r="A2" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B2" s="2">
         <f>'2019 Scenario'!B9</f>
@@ -11745,159 +11756,159 @@
       </c>
       <c r="F2" s="2">
         <f>'2019 Scenario'!F9</f>
-        <v>19615.2</v>
+        <v>29422.8</v>
       </c>
       <c r="G2" s="2">
         <f>'2019 Scenario'!G9</f>
-        <v>51763.65</v>
+        <v>77645.475</v>
       </c>
       <c r="H2" s="2">
         <f>'2019 Scenario'!H9</f>
-        <v>75710</v>
+        <v>113565</v>
       </c>
       <c r="I2" s="2">
         <f>'2019 Scenario'!I9</f>
-        <v>98949.559143541</v>
+        <v>148424.338715311</v>
       </c>
       <c r="J2" s="2">
         <f>'2019 Scenario'!J9</f>
-        <v>129322.615964881</v>
+        <v>193983.923947321</v>
       </c>
       <c r="K2" s="2">
         <f>'2019 Scenario'!K9</f>
-        <v>169018.832875636</v>
+        <v>253528.249313454</v>
       </c>
       <c r="L2" s="2">
         <f>'2019 Scenario'!L9</f>
-        <v>220900</v>
+        <v>331350</v>
       </c>
       <c r="M2" s="2">
         <f>'2019 Scenario'!M9</f>
-        <v>263309.084537545</v>
+        <v>394963.626806317</v>
       </c>
       <c r="N2" s="2">
         <f>'2019 Scenario'!N9</f>
-        <v>313860</v>
+        <v>470790</v>
       </c>
       <c r="O2" s="2">
         <f>'2019 Scenario'!O9</f>
-        <v>331269.11245362</v>
+        <v>496903.66868043</v>
       </c>
       <c r="P2" s="2">
         <f>'2019 Scenario'!P9</f>
-        <v>349643.86945074</v>
+        <v>524465.80417611</v>
       </c>
       <c r="Q2" s="2">
         <f>'2019 Scenario'!Q9</f>
-        <v>369037.833135144</v>
+        <v>553556.749702716</v>
       </c>
       <c r="R2" s="2">
         <f>'2019 Scenario'!R9</f>
-        <v>389507.536622973</v>
+        <v>584261.30493446</v>
       </c>
       <c r="S2" s="2">
         <f>'2019 Scenario'!S9</f>
-        <v>411112.648795923</v>
+        <v>616668.973193884</v>
       </c>
       <c r="T2" s="2">
         <f>'2019 Scenario'!T9</f>
-        <v>433916.148235144</v>
+        <v>650874.222352716</v>
       </c>
       <c r="U2" s="2">
         <f>'2019 Scenario'!U9</f>
-        <v>457984.506802873</v>
+        <v>686976.760204309</v>
       </c>
       <c r="V2" s="2">
         <f>'2019 Scenario'!V9</f>
-        <v>483387.883406923</v>
+        <v>725081.825110384</v>
       </c>
       <c r="W2" s="2">
         <f>'2019 Scenario'!W9</f>
-        <v>510200.328512858</v>
+        <v>765300.492769287</v>
       </c>
       <c r="X2" s="2">
         <f>'2019 Scenario'!X9</f>
-        <v>538500</v>
+        <v>807750</v>
       </c>
       <c r="Y2" s="2">
         <f>'2019 Scenario'!Y9</f>
-        <v>572741.202902248</v>
+        <v>859111.804353372</v>
       </c>
       <c r="Z2" s="2">
         <f>'2019 Scenario'!Z9</f>
-        <v>609159.675955273</v>
+        <v>913739.513932909</v>
       </c>
       <c r="AA2" s="2">
         <f>'2019 Scenario'!AA9</f>
-        <v>647893.863632621</v>
+        <v>971840.795448932</v>
       </c>
       <c r="AB2" s="2">
         <f>'2019 Scenario'!AB9</f>
-        <v>689091.01357462</v>
+        <v>1033636.52036193</v>
       </c>
       <c r="AC2" s="2">
         <f>'2019 Scenario'!AC9</f>
-        <v>732907.736348853</v>
+        <v>1099361.60452328</v>
       </c>
       <c r="AD2" s="2">
         <f>'2019 Scenario'!AD9</f>
-        <v>779510.600803725</v>
+        <v>1169265.90120559</v>
       </c>
       <c r="AE2" s="2">
         <f>'2019 Scenario'!AE9</f>
-        <v>829076.767278328</v>
+        <v>1243615.15091749</v>
       </c>
       <c r="AF2" s="2">
         <f>'2019 Scenario'!AF9</f>
-        <v>881794.66107576</v>
+        <v>1322691.99161364</v>
       </c>
       <c r="AG2" s="2">
         <f>'2019 Scenario'!AG9</f>
-        <v>937864.688760095</v>
+        <v>1406797.03314014</v>
       </c>
       <c r="AH2" s="2">
         <f>'2019 Scenario'!AH9</f>
-        <v>997500</v>
+        <v>1496250</v>
       </c>
       <c r="AI2" s="2">
         <f>'2019 Scenario'!AI9</f>
-        <v>1045403.78043856</v>
+        <v>1568105.67065784</v>
       </c>
       <c r="AJ2" s="2">
         <f>'2019 Scenario'!AJ9</f>
-        <v>1095608.08436616</v>
+        <v>1643412.12654924</v>
       </c>
       <c r="AK2" s="2">
         <f>'2019 Scenario'!AK9</f>
-        <v>1148223.39175482</v>
+        <v>1722335.08763223</v>
       </c>
       <c r="AL2" s="2">
         <f>'2019 Scenario'!AL9</f>
-        <v>1203365.48824911</v>
+        <v>1805048.23237367</v>
       </c>
       <c r="AM2" s="2">
         <f>'2019 Scenario'!AM9</f>
-        <v>1261155.71996483</v>
+        <v>1891733.57994724</v>
       </c>
       <c r="AN2" s="2">
         <f>'2019 Scenario'!AN9</f>
-        <v>1321721.26052426</v>
+        <v>1982581.89078639</v>
       </c>
       <c r="AO2" s="2">
         <f>'2019 Scenario'!AO9</f>
-        <v>1385195.39091538</v>
+        <v>2077793.08637307</v>
       </c>
       <c r="AP2" s="2">
         <f>'2019 Scenario'!AP9</f>
-        <v>1451717.79279099</v>
+        <v>2177576.68918649</v>
       </c>
       <c r="AQ2" s="2">
         <f>'2019 Scenario'!AQ9</f>
-        <v>1521434.85585326</v>
+        <v>2282152.28377989</v>
       </c>
       <c r="AR2" s="2">
         <f>'2019 Scenario'!AR9</f>
-        <v>1594500</v>
+        <v>2391750</v>
       </c>
     </row>
   </sheetData>
@@ -11919,15 +11930,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -17522,15 +17533,13 @@
   <sheetPr>
     <tabColor theme="7" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:AR11"/>
+  <dimension ref="A1:AR22"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.85"/>
   <cols>
-    <col min="7" max="7" width="9.53097345132743"/>
-    <col min="9" max="9" width="12.7964601769912"/>
-    <col min="10" max="10" width="11.6637168141593"/>
-    <col min="11" max="11" width="12.7964601769912"/>
-    <col min="13" max="13" width="12.7964601769912"/>
-    <col min="15" max="23" width="12.7964601769912"/>
+    <col min="1" max="1" width="11.3097345132743" customWidth="1"/>
+    <col min="4" max="4" width="12.7964601769912"/>
+    <col min="6" max="6" width="11.6637168141593"/>
+    <col min="7" max="23" width="12.7964601769912"/>
     <col min="24" max="24" width="9.53097345132743"/>
     <col min="25" max="25" width="12.7964601769912"/>
     <col min="26" max="26" width="11.6637168141593"/>
@@ -17691,16 +17700,16 @@
         <v>2726.7</v>
       </c>
       <c r="E2">
-        <f>D2+($H$2-$D$2)/($H$1-$D$1)</f>
-        <v>5927.5</v>
+        <f>E14</f>
+        <v>5730</v>
       </c>
       <c r="F2">
         <f>E2+($H$2-$D$2)/($H$1-$D$1)</f>
-        <v>9128.3</v>
+        <v>8930.8</v>
       </c>
       <c r="G2">
         <f>F2+($H$2-$D$2)/($H$1-$D$1)</f>
-        <v>12329.1</v>
+        <v>12131.6</v>
       </c>
       <c r="H2" s="21">
         <f>CNESA!N42</f>
@@ -17708,168 +17717,168 @@
       </c>
       <c r="I2" cm="1">
         <f t="array" ref="I2">FORECAST(I1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>18730.7000000002</v>
+        <v>18612.2000000002</v>
       </c>
       <c r="J2" cm="1">
         <f t="array" ref="J2">FORECAST(J1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>21931.5000000009</v>
+        <v>21813.0000000009</v>
       </c>
       <c r="K2" cm="1">
         <f t="array" ref="K2">FORECAST(K1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>25132.3000000007</v>
+        <v>25013.8000000007</v>
       </c>
       <c r="L2" cm="1">
         <f t="array" ref="L2">FORECAST(L1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>28333.1000000006</v>
+        <v>28214.6000000006</v>
       </c>
       <c r="M2" cm="1">
         <f t="array" ref="M2">FORECAST(M1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>31533.9000000004</v>
+        <v>31415.4000000004</v>
       </c>
       <c r="N2" cm="1">
         <f t="array" ref="N2">FORECAST(N1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>34734.7000000002</v>
+        <v>34616.2000000002</v>
       </c>
       <c r="O2" cm="1">
         <f t="array" ref="O2">FORECAST(O1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>37935.5000000009</v>
+        <v>37817.0000000009</v>
       </c>
       <c r="P2" cm="1">
         <f t="array" ref="P2">FORECAST(P1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>41136.3000000007</v>
+        <v>41017.8000000007</v>
       </c>
       <c r="Q2" cm="1">
         <f t="array" ref="Q2">FORECAST(Q1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>44337.1000000006</v>
+        <v>44218.6000000006</v>
       </c>
       <c r="R2" cm="1">
         <f t="array" ref="R2">FORECAST(R1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>47537.9000000004</v>
+        <v>47419.4000000004</v>
       </c>
       <c r="S2" cm="1">
         <f t="array" ref="S2">FORECAST(S1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>50738.7000000002</v>
+        <v>50620.2000000002</v>
       </c>
       <c r="T2" cm="1">
         <f t="array" ref="T2">FORECAST(T1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>53939.5000000009</v>
+        <v>53821.0000000009</v>
       </c>
       <c r="U2" cm="1">
         <f t="array" ref="U2">FORECAST(U1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>57140.3000000007</v>
+        <v>57021.8000000007</v>
       </c>
       <c r="V2" cm="1">
         <f t="array" ref="V2">FORECAST(V1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>60341.1000000006</v>
+        <v>60222.6000000006</v>
       </c>
       <c r="W2" cm="1">
         <f t="array" ref="W2">FORECAST(W1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>63541.9000000004</v>
+        <v>63423.4000000004</v>
       </c>
       <c r="X2" cm="1">
         <f t="array" ref="X2">FORECAST(X1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>66742.7000000002</v>
+        <v>66624.2000000002</v>
       </c>
       <c r="Y2" cm="1">
         <f t="array" ref="Y2">FORECAST(Y1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>69943.5000000009</v>
+        <v>69825.0000000009</v>
       </c>
       <c r="Z2" cm="1">
         <f t="array" ref="Z2">FORECAST(Z1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>73144.3000000007</v>
+        <v>73025.8000000007</v>
       </c>
       <c r="AA2" cm="1">
         <f t="array" ref="AA2">FORECAST(AA1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>76345.1000000006</v>
+        <v>76226.6000000006</v>
       </c>
       <c r="AB2" cm="1">
         <f t="array" ref="AB2">FORECAST(AB1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>79545.9000000004</v>
+        <v>79427.4000000004</v>
       </c>
       <c r="AC2" cm="1">
         <f t="array" ref="AC2">FORECAST(AC1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>82746.7000000002</v>
+        <v>82628.2000000002</v>
       </c>
       <c r="AD2" cm="1">
         <f t="array" ref="AD2">FORECAST(AD1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>85947.5000000009</v>
+        <v>85829.0000000009</v>
       </c>
       <c r="AE2" cm="1">
         <f t="array" ref="AE2">FORECAST(AE1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>89148.3000000007</v>
+        <v>89029.8000000007</v>
       </c>
       <c r="AF2" cm="1">
         <f t="array" ref="AF2">FORECAST(AF1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>92349.1000000006</v>
+        <v>92230.6000000006</v>
       </c>
       <c r="AG2" cm="1">
         <f t="array" ref="AG2">FORECAST(AG1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>95549.9000000004</v>
+        <v>95431.4000000004</v>
       </c>
       <c r="AH2" cm="1">
         <f t="array" ref="AH2">FORECAST(AH1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>98750.7000000002</v>
+        <v>98632.2000000002</v>
       </c>
       <c r="AI2" cm="1">
         <f t="array" ref="AI2">FORECAST(AI1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>101951.500000001</v>
+        <v>101833.000000001</v>
       </c>
       <c r="AJ2" cm="1">
         <f t="array" ref="AJ2">FORECAST(AJ1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>105152.300000001</v>
+        <v>105033.800000001</v>
       </c>
       <c r="AK2" cm="1">
         <f t="array" ref="AK2">FORECAST(AK1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>108353.100000001</v>
+        <v>108234.600000001</v>
       </c>
       <c r="AL2" cm="1">
         <f t="array" ref="AL2">FORECAST(AL1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>111553.9</v>
+        <v>111435.4</v>
       </c>
       <c r="AM2" cm="1">
         <f t="array" ref="AM2">FORECAST(AM1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>114754.7</v>
+        <v>114636.2</v>
       </c>
       <c r="AN2" cm="1">
         <f t="array" ref="AN2">FORECAST(AN1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>117955.500000001</v>
+        <v>117837.000000001</v>
       </c>
       <c r="AO2" cm="1">
         <f t="array" ref="AO2">FORECAST(AO1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>121156.300000001</v>
+        <v>121037.800000001</v>
       </c>
       <c r="AP2" cm="1">
         <f t="array" ref="AP2">FORECAST(AP1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>124357.100000001</v>
+        <v>124238.600000001</v>
       </c>
       <c r="AQ2" cm="1">
         <f t="array" ref="AQ2">FORECAST(AQ1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>127557.9</v>
+        <v>127439.4</v>
       </c>
       <c r="AR2" cm="1">
         <f t="array" ref="AR2">FORECAST(AR1,$D$2:$H$2,$D$1:$H$1)</f>
-        <v>130758.7</v>
+        <v>130640.2</v>
       </c>
     </row>
     <row r="3" spans="1:44">
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="22"/>
     </row>
     <row r="4" spans="1:44">
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="8" spans="1:44">
       <c r="B8">
@@ -18023,160 +18032,160 @@
         <v>11459.4</v>
       </c>
       <c r="F9">
-        <f>'CN LT Forecast'!D28</f>
-        <v>19615.2</v>
+        <f>'CN LT Forecast'!D28*1.5</f>
+        <v>29422.8</v>
       </c>
       <c r="G9">
-        <f>'CN LT Forecast'!E28</f>
-        <v>51763.65</v>
+        <f>'CN LT Forecast'!E28*1.5</f>
+        <v>77645.475</v>
       </c>
       <c r="H9">
-        <f>'CN LT Forecast'!F28</f>
-        <v>75710</v>
+        <f>'CN LT Forecast'!F28*1.5</f>
+        <v>113565</v>
       </c>
       <c r="I9">
-        <f>'CN LT Forecast'!G28</f>
-        <v>98949.559143541</v>
+        <f>'CN LT Forecast'!G28*1.5</f>
+        <v>148424.338715311</v>
       </c>
       <c r="J9">
-        <f>'CN LT Forecast'!H28</f>
-        <v>129322.615964881</v>
+        <f>'CN LT Forecast'!H28*1.5</f>
+        <v>193983.923947321</v>
       </c>
       <c r="K9">
-        <f>'CN LT Forecast'!I28</f>
-        <v>169018.832875636</v>
+        <f>'CN LT Forecast'!I28*1.5</f>
+        <v>253528.249313454</v>
       </c>
       <c r="L9">
-        <f>'CN LT Forecast'!J28</f>
-        <v>220900</v>
+        <f>'CN LT Forecast'!J28*1.5</f>
+        <v>331350</v>
       </c>
       <c r="M9">
-        <f>'CN LT Forecast'!K28</f>
-        <v>263309.084537545</v>
+        <f>'CN LT Forecast'!K28*1.5</f>
+        <v>394963.626806317</v>
       </c>
       <c r="N9">
-        <f>'CN LT Forecast'!L28</f>
-        <v>313860</v>
+        <f>'CN LT Forecast'!L28*1.5</f>
+        <v>470790</v>
       </c>
       <c r="O9">
-        <f>'CN LT Forecast'!M28</f>
-        <v>331269.11245362</v>
+        <f>'CN LT Forecast'!M28*1.5</f>
+        <v>496903.66868043</v>
       </c>
       <c r="P9">
-        <f>'CN LT Forecast'!N28</f>
-        <v>349643.86945074</v>
+        <f>'CN LT Forecast'!N28*1.5</f>
+        <v>524465.80417611</v>
       </c>
       <c r="Q9">
-        <f>'CN LT Forecast'!O28</f>
-        <v>369037.833135144</v>
+        <f>'CN LT Forecast'!O28*1.5</f>
+        <v>553556.749702716</v>
       </c>
       <c r="R9">
-        <f>'CN LT Forecast'!P28</f>
-        <v>389507.536622973</v>
+        <f>'CN LT Forecast'!P28*1.5</f>
+        <v>584261.30493446</v>
       </c>
       <c r="S9">
-        <f>'CN LT Forecast'!Q28</f>
-        <v>411112.648795923</v>
+        <f>'CN LT Forecast'!Q28*1.5</f>
+        <v>616668.973193884</v>
       </c>
       <c r="T9">
-        <f>'CN LT Forecast'!R28</f>
-        <v>433916.148235144</v>
+        <f>'CN LT Forecast'!R28*1.5</f>
+        <v>650874.222352716</v>
       </c>
       <c r="U9">
-        <f>'CN LT Forecast'!S28</f>
-        <v>457984.506802873</v>
+        <f>'CN LT Forecast'!S28*1.5</f>
+        <v>686976.760204309</v>
       </c>
       <c r="V9">
-        <f>'CN LT Forecast'!T28</f>
-        <v>483387.883406923</v>
+        <f>'CN LT Forecast'!T28*1.5</f>
+        <v>725081.825110384</v>
       </c>
       <c r="W9">
-        <f>'CN LT Forecast'!U28</f>
-        <v>510200.328512858</v>
+        <f>'CN LT Forecast'!U28*1.5</f>
+        <v>765300.492769287</v>
       </c>
       <c r="X9">
-        <f>'CN LT Forecast'!V28</f>
-        <v>538500</v>
+        <f>'CN LT Forecast'!V28*1.5</f>
+        <v>807750</v>
       </c>
       <c r="Y9">
-        <f>'CN LT Forecast'!W28</f>
-        <v>572741.202902248</v>
+        <f>'CN LT Forecast'!W28*1.5</f>
+        <v>859111.804353372</v>
       </c>
       <c r="Z9">
-        <f>'CN LT Forecast'!X28</f>
-        <v>609159.675955273</v>
+        <f>'CN LT Forecast'!X28*1.5</f>
+        <v>913739.513932909</v>
       </c>
       <c r="AA9">
-        <f>'CN LT Forecast'!Y28</f>
-        <v>647893.863632621</v>
+        <f>'CN LT Forecast'!Y28*1.5</f>
+        <v>971840.795448932</v>
       </c>
       <c r="AB9">
-        <f>'CN LT Forecast'!Z28</f>
-        <v>689091.01357462</v>
+        <f>'CN LT Forecast'!Z28*1.5</f>
+        <v>1033636.52036193</v>
       </c>
       <c r="AC9">
-        <f>'CN LT Forecast'!AA28</f>
-        <v>732907.736348853</v>
+        <f>'CN LT Forecast'!AA28*1.5</f>
+        <v>1099361.60452328</v>
       </c>
       <c r="AD9">
-        <f>'CN LT Forecast'!AB28</f>
-        <v>779510.600803725</v>
+        <f>'CN LT Forecast'!AB28*1.5</f>
+        <v>1169265.90120559</v>
       </c>
       <c r="AE9">
-        <f>'CN LT Forecast'!AC28</f>
-        <v>829076.767278328</v>
+        <f>'CN LT Forecast'!AC28*1.5</f>
+        <v>1243615.15091749</v>
       </c>
       <c r="AF9">
-        <f>'CN LT Forecast'!AD28</f>
-        <v>881794.66107576</v>
+        <f>'CN LT Forecast'!AD28*1.5</f>
+        <v>1322691.99161364</v>
       </c>
       <c r="AG9">
-        <f>'CN LT Forecast'!AE28</f>
-        <v>937864.688760095</v>
+        <f>'CN LT Forecast'!AE28*1.5</f>
+        <v>1406797.03314014</v>
       </c>
       <c r="AH9">
-        <f>'CN LT Forecast'!AF28</f>
-        <v>997500</v>
+        <f>'CN LT Forecast'!AF28*1.5</f>
+        <v>1496250</v>
       </c>
       <c r="AI9">
-        <f>'CN LT Forecast'!AG28</f>
-        <v>1045403.78043856</v>
+        <f>'CN LT Forecast'!AG28*1.5</f>
+        <v>1568105.67065784</v>
       </c>
       <c r="AJ9">
-        <f>'CN LT Forecast'!AH28</f>
-        <v>1095608.08436616</v>
+        <f>'CN LT Forecast'!AH28*1.5</f>
+        <v>1643412.12654924</v>
       </c>
       <c r="AK9">
-        <f>'CN LT Forecast'!AI28</f>
-        <v>1148223.39175482</v>
+        <f>'CN LT Forecast'!AI28*1.5</f>
+        <v>1722335.08763223</v>
       </c>
       <c r="AL9">
-        <f>'CN LT Forecast'!AJ28</f>
-        <v>1203365.48824911</v>
+        <f>'CN LT Forecast'!AJ28*1.5</f>
+        <v>1805048.23237367</v>
       </c>
       <c r="AM9">
-        <f>'CN LT Forecast'!AK28</f>
-        <v>1261155.71996483</v>
+        <f>'CN LT Forecast'!AK28*1.5</f>
+        <v>1891733.57994724</v>
       </c>
       <c r="AN9">
-        <f>'CN LT Forecast'!AL28</f>
-        <v>1321721.26052426</v>
+        <f>'CN LT Forecast'!AL28*1.5</f>
+        <v>1982581.89078639</v>
       </c>
       <c r="AO9">
-        <f>'CN LT Forecast'!AM28</f>
-        <v>1385195.39091538</v>
+        <f>'CN LT Forecast'!AM28*1.5</f>
+        <v>2077793.08637307</v>
       </c>
       <c r="AP9">
-        <f>'CN LT Forecast'!AN28</f>
-        <v>1451717.79279099</v>
+        <f>'CN LT Forecast'!AN28*1.5</f>
+        <v>2177576.68918649</v>
       </c>
       <c r="AQ9">
-        <f>'CN LT Forecast'!AO28</f>
-        <v>1521434.85585326</v>
+        <f>'CN LT Forecast'!AO28*1.5</f>
+        <v>2282152.28377989</v>
       </c>
       <c r="AR9">
-        <f>'CN LT Forecast'!AP28</f>
-        <v>1594500</v>
+        <f>'CN LT Forecast'!AP28*1.5</f>
+        <v>2391750</v>
       </c>
     </row>
     <row r="10" spans="1:44">
@@ -18186,12 +18195,289 @@
       <c r="E10" s="22"/>
     </row>
     <row r="11" spans="1:44">
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+    </row>
+    <row r="14" spans="1:44">
+      <c r="A14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14">
+        <v>3269</v>
+      </c>
+      <c r="E14">
+        <v>5730</v>
+      </c>
+      <c r="F14">
+        <v>13100</v>
+      </c>
+      <c r="G14">
+        <v>34500</v>
+      </c>
+      <c r="H14">
+        <v>78300</v>
+      </c>
+      <c r="I14">
+        <v>144700</v>
+      </c>
+      <c r="J14">
+        <f>(I14+K14)/2</f>
+        <v>162350</v>
+      </c>
+      <c r="K14">
+        <v>180000</v>
+      </c>
+      <c r="L14">
+        <f>K14+($N$14-$K$14)/($N$1-$K$1)</f>
+        <v>220000</v>
+      </c>
+      <c r="M14">
+        <f>L14+($N$14-$K$14)/($N$1-$K$1)</f>
+        <v>260000</v>
+      </c>
+      <c r="N14">
+        <v>300000</v>
+      </c>
+      <c r="O14" cm="1">
+        <f t="array" ref="O14">FORECAST(O1,$G$14:$N$14,$G$1:$N$1)</f>
+        <v>333760.714285716</v>
+      </c>
+      <c r="P14" cm="1">
+        <f t="array" ref="P14">FORECAST(P1,$G$14:$N$14,$G$1:$N$1)</f>
+        <v>369600.595238104</v>
+      </c>
+      <c r="Q14" cm="1">
+        <f t="array" ref="Q14">FORECAST(Q1,$G$14:$N$14,$G$1:$N$1)</f>
+        <v>405440.476190478</v>
+      </c>
+      <c r="R14" cm="1">
+        <f t="array" ref="R14">FORECAST(R1,$G$14:$N$14,$G$1:$N$1)</f>
+        <v>441280.357142866</v>
+      </c>
+      <c r="S14" cm="1">
+        <f t="array" ref="S14">FORECAST(S1,$G$14:$N$14,$G$1:$N$1)</f>
+        <v>477120.238095239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44">
+      <c r="A16" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16">
+        <f>D14-D2</f>
+        <v>542.3</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ref="E16:S16" si="0">E14-E2</f>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>4169.2</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>22368.4</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>62770.1</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>126087.8</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>140536.999999999</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>154986.199999999</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>191785.399999999</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="0"/>
+        <v>228584.6</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="0"/>
+        <v>265383.8</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>295943.714285715</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="0"/>
+        <v>328582.795238104</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="0"/>
+        <v>361221.876190477</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="0"/>
+        <v>393860.957142865</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="0"/>
+        <v>426500.038095239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="24">
+        <f>D16/D9</f>
+        <v>0.0829407806191117</v>
+      </c>
+      <c r="E18" s="24">
+        <f t="shared" ref="E18:S18" si="1">E16/E9</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.141699634297212</v>
+      </c>
+      <c r="G18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.288083755041746</v>
+      </c>
+      <c r="H18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.552723990666138</v>
+      </c>
+      <c r="I18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.849508922130657</v>
+      </c>
+      <c r="J18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.724477560512507</v>
+      </c>
+      <c r="K18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.611317280893536</v>
+      </c>
+      <c r="L18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.578800060359135</v>
+      </c>
+      <c r="M18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.578748483368807</v>
+      </c>
+      <c r="N18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.563698889101297</v>
+      </c>
+      <c r="O18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.595575627508686</v>
+      </c>
+      <c r="P18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.6265094742531</v>
+      </c>
+      <c r="Q18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.65254714423493</v>
+      </c>
+      <c r="R18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.67411781991458</v>
+      </c>
+      <c r="S18" s="24">
+        <f t="shared" si="1"/>
+        <v>0.691619096524813</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" s="25">
+        <f>D18/(MAX($D$18:$S$18))</f>
+        <v>0.0976337957829655</v>
+      </c>
+      <c r="E20" s="25">
+        <f t="shared" ref="E20:S20" si="2">E18/(MAX($D$18:$S$18))</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.166801819975962</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.339117986329327</v>
+      </c>
+      <c r="H20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.650639417982626</v>
+      </c>
+      <c r="I20" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.852819248437605</v>
+      </c>
+      <c r="K20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.719612549048089</v>
+      </c>
+      <c r="L20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.681334880989177</v>
+      </c>
+      <c r="M20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.681274167100264</v>
+      </c>
+      <c r="N20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.663558527069359</v>
+      </c>
+      <c r="O20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.701082251160965</v>
+      </c>
+      <c r="P20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.737496049696274</v>
+      </c>
+      <c r="Q20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.768146310456956</v>
+      </c>
+      <c r="R20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.793538245865413</v>
+      </c>
+      <c r="S20" s="25">
+        <f t="shared" si="2"/>
+        <v>0.814139885417754</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22">
+        <f>MAX(D18:S18)</f>
+        <v>0.849508922130657</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18213,32 +18499,32 @@
     </row>
     <row r="2" spans="2:14">
       <c r="M2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="M3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="2:14">
       <c r="M4" s="17" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="2:14">
       <c r="M5" s="18" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="2:14">
       <c r="M6" s="17" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="2:14">
       <c r="M7" s="18" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="2:14">
@@ -18246,7 +18532,7 @@
         <v>2022</v>
       </c>
       <c r="N9" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="2:14">
@@ -18272,7 +18558,7 @@
         <v>2025</v>
       </c>
       <c r="Q68" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="R68">
         <v>2021</v>
@@ -18292,7 +18578,7 @@
     </row>
     <row r="69" spans="10:24">
       <c r="J69" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K69">
         <v>495</v>
@@ -18330,7 +18616,7 @@
     </row>
     <row r="70" spans="10:24">
       <c r="J70" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K70">
         <v>260</v>
@@ -18372,7 +18658,7 @@
     </row>
     <row r="71" spans="10:24">
       <c r="J71" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K71">
         <v>122</v>
@@ -18414,7 +18700,7 @@
     </row>
     <row r="72" spans="10:24">
       <c r="J72" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K72">
         <v>113</v>
@@ -18460,10 +18746,10 @@
     </row>
     <row r="74" spans="10:24">
       <c r="J74" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q74" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="R74">
         <v>2021</v>
@@ -18481,12 +18767,12 @@
         <v>2025</v>
       </c>
       <c r="W74" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="10:24">
       <c r="J75" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K75">
         <f>K70/2</f>
@@ -18543,7 +18829,7 @@
     </row>
     <row r="76" spans="10:24">
       <c r="J76" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K76">
         <f>K71/2</f>
@@ -18600,7 +18886,7 @@
     </row>
     <row r="77" spans="10:24">
       <c r="J77" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K77">
         <f>K72/2</f>
@@ -18721,7 +19007,7 @@
     </row>
     <row r="82" spans="15:24">
       <c r="P82" s="6" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -18946,7 +19232,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B4">
         <v>24000</v>
@@ -18986,12 +19272,12 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B7">
         <f>B5*1.5</f>
@@ -19016,7 +19302,7 @@
     </row>
     <row r="24" spans="1:42">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:42">
@@ -19146,7 +19432,7 @@
     </row>
     <row r="27" spans="1:42">
       <c r="A27" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B27" s="7">
         <f>CNESA!J38</f>
@@ -19315,7 +19601,7 @@
     </row>
     <row r="28" s="6" customFormat="1" spans="1:42">
       <c r="A28" s="6" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B28" s="7">
         <f>MAX(CNESA!J34:J44)*1.5</f>
@@ -19495,7 +19781,7 @@
     </row>
     <row r="30" s="6" customFormat="1" spans="1:42">
       <c r="A30" s="6" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B30" s="9">
         <f>B27</f>
@@ -19664,7 +19950,7 @@
     </row>
     <row r="31" s="6" customFormat="1" spans="1:42">
       <c r="A31" s="6" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B31" s="9">
         <f>B30-B27</f>
@@ -19833,7 +20119,7 @@
     </row>
     <row r="32" s="6" customFormat="1" spans="1:42">
       <c r="A32" s="6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B32" s="11">
         <f>B31/B28</f>
@@ -20002,7 +20288,7 @@
     </row>
     <row r="33" s="6" customFormat="1" spans="1:42">
       <c r="A33" s="6" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B33" s="13">
         <f>MAX(B32:AP32)</f>
@@ -20019,7 +20305,7 @@
     </row>
     <row r="34" spans="1:42">
       <c r="A34" s="14" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="B34" s="15">
         <f t="shared" ref="B34:AP34" si="19">B32/$B$33</f>
@@ -20199,7 +20485,7 @@
     </row>
     <row r="39" spans="1:42">
       <c r="A39" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D39">
         <f>D36</f>
@@ -20381,7 +20667,7 @@
   <sheetData>
     <row r="1" spans="1:44">
       <c r="A1" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B1" s="4">
         <v>2018</v>
@@ -20515,7 +20801,7 @@
     </row>
     <row r="2" spans="1:44">
       <c r="A2" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B2" s="4">
         <f>'2019 Scenario'!B2</f>
@@ -20531,15 +20817,15 @@
       </c>
       <c r="E2" s="4">
         <f>'2019 Scenario'!E2</f>
-        <v>5927.5</v>
+        <v>5730</v>
       </c>
       <c r="F2" s="4">
         <f>'2019 Scenario'!F2</f>
-        <v>9128.3</v>
+        <v>8930.8</v>
       </c>
       <c r="G2" s="4">
         <f>'2019 Scenario'!G2</f>
-        <v>12329.1</v>
+        <v>12131.6</v>
       </c>
       <c r="H2" s="4">
         <f>'2019 Scenario'!H2</f>
@@ -20547,147 +20833,147 @@
       </c>
       <c r="I2" s="4">
         <f>'2019 Scenario'!I2</f>
-        <v>18730.7000000002</v>
+        <v>18612.2000000002</v>
       </c>
       <c r="J2" s="4">
         <f>'2019 Scenario'!J2</f>
-        <v>21931.5000000009</v>
+        <v>21813.0000000009</v>
       </c>
       <c r="K2" s="4">
         <f>'2019 Scenario'!K2</f>
-        <v>25132.3000000007</v>
+        <v>25013.8000000007</v>
       </c>
       <c r="L2" s="4">
         <f>'2019 Scenario'!L2</f>
-        <v>28333.1000000006</v>
+        <v>28214.6000000006</v>
       </c>
       <c r="M2" s="4">
         <f>'2019 Scenario'!M2</f>
-        <v>31533.9000000004</v>
+        <v>31415.4000000004</v>
       </c>
       <c r="N2" s="4">
         <f>'2019 Scenario'!N2</f>
-        <v>34734.7000000002</v>
+        <v>34616.2000000002</v>
       </c>
       <c r="O2" s="4">
         <f>'2019 Scenario'!O2</f>
-        <v>37935.5000000009</v>
+        <v>37817.0000000009</v>
       </c>
       <c r="P2" s="4">
         <f>'2019 Scenario'!P2</f>
-        <v>41136.3000000007</v>
+        <v>41017.8000000007</v>
       </c>
       <c r="Q2" s="4">
         <f>'2019 Scenario'!Q2</f>
-        <v>44337.1000000006</v>
+        <v>44218.6000000006</v>
       </c>
       <c r="R2" s="4">
         <f>'2019 Scenario'!R2</f>
-        <v>47537.9000000004</v>
+        <v>47419.4000000004</v>
       </c>
       <c r="S2" s="4">
         <f>'2019 Scenario'!S2</f>
-        <v>50738.7000000002</v>
+        <v>50620.2000000002</v>
       </c>
       <c r="T2" s="4">
         <f>'2019 Scenario'!T2</f>
-        <v>53939.5000000009</v>
+        <v>53821.0000000009</v>
       </c>
       <c r="U2" s="4">
         <f>'2019 Scenario'!U2</f>
-        <v>57140.3000000007</v>
+        <v>57021.8000000007</v>
       </c>
       <c r="V2" s="4">
         <f>'2019 Scenario'!V2</f>
-        <v>60341.1000000006</v>
+        <v>60222.6000000006</v>
       </c>
       <c r="W2" s="4">
         <f>'2019 Scenario'!W2</f>
-        <v>63541.9000000004</v>
+        <v>63423.4000000004</v>
       </c>
       <c r="X2" s="4">
         <f>'2019 Scenario'!X2</f>
-        <v>66742.7000000002</v>
+        <v>66624.2000000002</v>
       </c>
       <c r="Y2" s="4">
         <f>'2019 Scenario'!Y2</f>
-        <v>69943.5000000009</v>
+        <v>69825.0000000009</v>
       </c>
       <c r="Z2" s="4">
         <f>'2019 Scenario'!Z2</f>
-        <v>73144.3000000007</v>
+        <v>73025.8000000007</v>
       </c>
       <c r="AA2" s="4">
         <f>'2019 Scenario'!AA2</f>
-        <v>76345.1000000006</v>
+        <v>76226.6000000006</v>
       </c>
       <c r="AB2" s="4">
         <f>'2019 Scenario'!AB2</f>
-        <v>79545.9000000004</v>
+        <v>79427.4000000004</v>
       </c>
       <c r="AC2" s="4">
         <f>'2019 Scenario'!AC2</f>
-        <v>82746.7000000002</v>
+        <v>82628.2000000002</v>
       </c>
       <c r="AD2" s="4">
         <f>'2019 Scenario'!AD2</f>
-        <v>85947.5000000009</v>
+        <v>85829.0000000009</v>
       </c>
       <c r="AE2" s="4">
         <f>'2019 Scenario'!AE2</f>
-        <v>89148.3000000007</v>
+        <v>89029.8000000007</v>
       </c>
       <c r="AF2" s="4">
         <f>'2019 Scenario'!AF2</f>
-        <v>92349.1000000006</v>
+        <v>92230.6000000006</v>
       </c>
       <c r="AG2" s="4">
         <f>'2019 Scenario'!AG2</f>
-        <v>95549.9000000004</v>
+        <v>95431.4000000004</v>
       </c>
       <c r="AH2" s="4">
         <f>'2019 Scenario'!AH2</f>
-        <v>98750.7000000002</v>
+        <v>98632.2000000002</v>
       </c>
       <c r="AI2" s="4">
         <f>'2019 Scenario'!AI2</f>
-        <v>101951.500000001</v>
+        <v>101833.000000001</v>
       </c>
       <c r="AJ2" s="4">
         <f>'2019 Scenario'!AJ2</f>
-        <v>105152.300000001</v>
+        <v>105033.800000001</v>
       </c>
       <c r="AK2" s="4">
         <f>'2019 Scenario'!AK2</f>
-        <v>108353.100000001</v>
+        <v>108234.600000001</v>
       </c>
       <c r="AL2" s="4">
         <f>'2019 Scenario'!AL2</f>
-        <v>111553.9</v>
+        <v>111435.4</v>
       </c>
       <c r="AM2" s="4">
         <f>'2019 Scenario'!AM2</f>
-        <v>114754.7</v>
+        <v>114636.2</v>
       </c>
       <c r="AN2" s="4">
         <f>'2019 Scenario'!AN2</f>
-        <v>117955.500000001</v>
+        <v>117837.000000001</v>
       </c>
       <c r="AO2" s="4">
         <f>'2019 Scenario'!AO2</f>
-        <v>121156.300000001</v>
+        <v>121037.800000001</v>
       </c>
       <c r="AP2" s="4">
         <f>'2019 Scenario'!AP2</f>
-        <v>124357.100000001</v>
+        <v>124238.600000001</v>
       </c>
       <c r="AQ2" s="4">
         <f>'2019 Scenario'!AQ2</f>
-        <v>127557.9</v>
+        <v>127439.4</v>
       </c>
       <c r="AR2" s="4">
         <f>'2019 Scenario'!AR2</f>
-        <v>130758.7</v>
+        <v>130640.2</v>
       </c>
     </row>
   </sheetData>
